--- a/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
+++ b/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
@@ -40,7 +40,7 @@
     <t>Ausência de informações inventadas</t>
   </si>
   <si>
-    <t>Não adiciona dados inexistentes; todos os valores correspondem aos documentos originais.</t>
+    <t>Não adiciona dados inexistentes. A maioria dos valores corresponde aos documentos originais, com pequenas divergências numéricas pontuais</t>
   </si>
   <si>
     <t>B. Qualidade dos Resumos Individuais</t>
@@ -162,7 +162,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -424,8 +423,8 @@
     <col customWidth="1" min="1" max="1" width="15.43"/>
     <col customWidth="1" min="2" max="2" width="33.29"/>
     <col customWidth="1" min="3" max="3" width="32.0"/>
-    <col customWidth="1" min="4" max="4" width="78.71"/>
-    <col customWidth="1" min="5" max="25" width="8.71"/>
+    <col customWidth="1" min="4" max="4" width="122.57"/>
+    <col customWidth="1" min="5" max="6" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,7 +465,7 @@
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -555,7 +554,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -569,7 +568,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -583,7 +582,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -597,7 +596,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -611,7 +610,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -625,7 +624,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -639,7 +638,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -653,7 +652,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">

--- a/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
+++ b/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
@@ -34,13 +34,13 @@
     <t>Preservação de informações-chave</t>
   </si>
   <si>
-    <t>Resumo mantém corretamente todos os pontos essenciais presentes nos balancetes.</t>
+    <t>Resumo preserva os principais pontos dos balancetes, mas apresenta divergências numéricas e algumas interpretações que extrapolam os dados.</t>
   </si>
   <si>
     <t>Ausência de informações inventadas</t>
   </si>
   <si>
-    <t>Não adiciona dados inexistentes. A maioria dos valores corresponde aos documentos originais, com pequenas divergências numéricas pontuais</t>
+    <t>Não inventa os dados-base dos documentos, mas apresenta divergências numéricas pontuais e inclui recomendações que extrapolam a evidência dos balancetes.</t>
   </si>
   <si>
     <t>B. Qualidade dos Resumos Individuais</t>
@@ -55,7 +55,7 @@
     <t>Coerência interna</t>
   </si>
   <si>
-    <t>Fluxo lógico bem estruturado, apresentando evolução natural dos insights.</t>
+    <t>O texto é bem organizado, mas a progressão analítica é enfraquecida por inferências e recomendações que vão além dos balancetes.</t>
   </si>
   <si>
     <t>C. Qualidade da Análise Consolidada</t>
@@ -64,13 +64,13 @@
     <t>Identificação de padrões válidos</t>
   </si>
   <si>
-    <t>Padrões descritos condizem com os dados apresentados nos balancetes.</t>
+    <t>Os padrões gerais descritos condizem com os balancetes, mas algumas leituras específicas sobre variações e tendências carecem de maior precisão.</t>
   </si>
   <si>
     <t>Conclusões fundamentadas</t>
   </si>
   <si>
-    <t>Conclusões derivam diretamente dos resultados mensais analisados.</t>
+    <t>Parte das conclusões deriva dos resultados mensais, mas várias recomendações e metas propostas extrapolam o que os balancetes sustentam diretamente.</t>
   </si>
   <si>
     <t>D. Estrutura e Organização</t>
@@ -91,62 +91,66 @@
     <t>Llama 8B</t>
   </si>
   <si>
-    <t>Mantém bem os elementos principais, embora com algumas reorganizações.</t>
-  </si>
-  <si>
-    <t>Alguns valores divergiram ligeiramente, mas sem inventar categorias.</t>
+    <t>Preserva apenas parte das informações centrais. O relatório apresenta recorte temporal mal formulado, ordem dos períodos inconsistente e síntese com distorções relevantes dos dados.</t>
+  </si>
+  <si>
+    <t>Não inventa categorias nem a base temática dos documentos, mas apresenta erros numéricos relevantes em resultados e margens.</t>
   </si>
   <si>
     <t>Resumo ligeiramente mais enxuto, mas ainda apropriado.</t>
   </si>
   <si>
-    <t>Boa fluidez, embora algumas transições sejam abruptas.</t>
+    <t>A fluidez do texto é apenas aparente. A análise é incoerente porque erra a ordem dos períodos, compara dados de forma inadequada e apresenta métricas incorretas.</t>
   </si>
   <si>
     <t>Padrões identificados condizem parcialmente com os balancetes.</t>
   </si>
   <si>
-    <t>Conclusões são apoiadas pelos dados, mas algumas interpretações são generalizadas.</t>
+    <t>Parte das conclusões se apoia nos balancetes, mas várias interpretações são generalizadas e algumas dependem de cálculos incorretos.</t>
   </si>
   <si>
     <t>Segue organização semelhante aos demais modelos.</t>
   </si>
   <si>
-    <t>Pequenas inconsistências em margens percentuais observadas.</t>
+    <t>Há inconsistências relevantes em métricas consolidadas, incluindo resultados, margens e organização temporal dos períodos analisados.</t>
   </si>
   <si>
     <t>Llama 70B</t>
   </si>
   <si>
-    <t>Preserva corretamente dados essenciais, embora enfatize outros aspectos.</t>
-  </si>
-  <si>
-    <t>Não inventa dados, mas ajusta alguns valores percentuais.</t>
+    <t>Preserva só parte dos dados. A análise é comprometida por desordem dos períodos e interpretação errada das margens.</t>
+  </si>
+  <si>
+    <t>Não inventa os dados-base, mas apresenta margens imprecisas e usa essas imprecisões para sustentar conclusões analíticas frágeis.</t>
   </si>
   <si>
     <t>Resumo sintético, com boa distribuição de informações.</t>
   </si>
   <si>
-    <t>Boa coerência, mantendo linha lógica.</t>
-  </si>
-  <si>
-    <t>Padrões descritos existem, mas algumas análises exageram tendências.</t>
-  </si>
-  <si>
-    <t>Conclusões coerentes, embora nem sempre totalmente sustentadas.</t>
+    <t>A coerência é apenas aparente: a tabela está fora de ordem cronológica e as conclusões 
+contradizem os próprios números do relatório.</t>
+  </si>
+  <si>
+    <t>O relatório força conclusões. Trata fatos básicos dos balancetes como tendências 
+e diagnósticos sólidos, sem base suficiente nos dados.</t>
+  </si>
+  <si>
+    <t>As conclusões são fracas e mal sustentadas.</t>
   </si>
   <si>
     <t>Segue estrutura esperada de relatório financeiro.</t>
   </si>
   <si>
-    <t>Inclui metas e números coerentes, mas com pequenas variações.</t>
+    <t>Os metadados temporais e a organização dos períodos estão inadequados. 
+A tabela fora de ordem compromete a leitura evolutiva e sustenta comparações 
+mal formuladas.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -162,6 +166,16 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -192,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -201,7 +215,19 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -423,7 +449,7 @@
     <col customWidth="1" min="1" max="1" width="15.43"/>
     <col customWidth="1" min="2" max="2" width="33.29"/>
     <col customWidth="1" min="3" max="3" width="32.0"/>
-    <col customWidth="1" min="4" max="4" width="122.57"/>
+    <col customWidth="1" min="4" max="4" width="71.43"/>
     <col customWidth="1" min="5" max="6" width="8.71"/>
   </cols>
   <sheetData>
@@ -451,7 +477,7 @@
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -493,7 +519,7 @@
       <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -507,7 +533,7 @@
       <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -521,7 +547,7 @@
       <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -563,7 +589,7 @@
       <c r="C10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -577,7 +603,7 @@
       <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -591,7 +617,7 @@
       <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -605,7 +631,7 @@
       <c r="C13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>29</v>
       </c>
     </row>
@@ -633,7 +659,7 @@
       <c r="C15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -661,7 +687,7 @@
       <c r="C17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -675,7 +701,7 @@
       <c r="C18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -689,7 +715,7 @@
       <c r="C19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -707,7 +733,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21">
       <c r="A21" s="2" t="s">
         <v>34</v>
       </c>
@@ -717,11 +743,11 @@
       <c r="C21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22">
       <c r="A22" s="2" t="s">
         <v>34</v>
       </c>
@@ -731,11 +757,11 @@
       <c r="C22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23">
       <c r="A23" s="2" t="s">
         <v>34</v>
       </c>
@@ -745,11 +771,11 @@
       <c r="C23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24">
       <c r="A24" s="2" t="s">
         <v>34</v>
       </c>
@@ -763,7 +789,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25">
       <c r="A25" s="2" t="s">
         <v>34</v>
       </c>
@@ -773,7 +799,7 @@
       <c r="C25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="7" t="s">
         <v>42</v>
       </c>
     </row>

--- a/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
+++ b/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
@@ -34,13 +34,13 @@
     <t>Preservação de informações-chave</t>
   </si>
   <si>
-    <t>Resumo preserva os principais pontos dos balancetes, mas apresenta divergências numéricas e algumas interpretações que extrapolam os dados.</t>
+    <t>Preserva os principais pontos dos balancetes e apresenta boa organização analítica, mas contém erros numéricos em junho e agosto, além de pequena imprecisão na margem de setembro, o que compromete parcialmente a comparação entre os períodos.</t>
   </si>
   <si>
     <t>Ausência de informações inventadas</t>
   </si>
   <si>
-    <t>Não inventa os dados-base dos documentos, mas apresenta divergências numéricas pontuais e inclui recomendações que extrapolam a evidência dos balancetes.</t>
+    <t>Não inventa categorias, períodos ou estrutura documental, mas apresenta incorreções parciais nos valores consolidados: resultado e margem em junho e agosto, além de pequena imprecisão na margem de setembro.</t>
   </si>
   <si>
     <t>B. Qualidade dos Resumos Individuais</t>
@@ -49,13 +49,13 @@
     <t>Concisão adequada</t>
   </si>
   <si>
-    <t>Resumo bem equilibrado, sem excesso ou falta de detalhes.</t>
+    <t>O relatório apresenta boa concisão, com síntese clara e sem excesso de detalhamento.</t>
   </si>
   <si>
     <t>Coerência interna</t>
   </si>
   <si>
-    <t>O texto é bem organizado, mas a progressão analítica é enfraquecida por inferências e recomendações que vão além dos balancetes.</t>
+    <t>O relatório apresenta boa coerência discursiva e linguagem cautelosa, mas a coerência analítica é parcialmente enfraquecida por erros numéricos que afetam comparações de desempenho.</t>
   </si>
   <si>
     <t>C. Qualidade da Análise Consolidada</t>
@@ -64,13 +64,13 @@
     <t>Identificação de padrões válidos</t>
   </si>
   <si>
-    <t>Os padrões gerais descritos condizem com os balancetes, mas algumas leituras específicas sobre variações e tendências carecem de maior precisão.</t>
+    <t>Identifica de forma adequada os padrões gerais da série, como oscilação das receitas, estabilidade relativa das despesas e recorrência de categorias de gasto, embora parte da comparação entre períodos fique comprometida por erros de cálculo.</t>
   </si>
   <si>
     <t>Conclusões fundamentadas</t>
   </si>
   <si>
-    <t>Parte das conclusões deriva dos resultados mensais, mas várias recomendações e metas propostas extrapolam o que os balancetes sustentam diretamente.</t>
+    <t>As conclusões são cautelosas e bem fundamentadas, com uso de pontos para investigação e explicitação das limitações da análise.</t>
   </si>
   <si>
     <t>D. Estrutura e Organização</t>
@@ -79,71 +79,67 @@
     <t>Aderência ao formato</t>
   </si>
   <si>
-    <t>Segue estrutura clara com resumo, dados, insights e recomendações.</t>
+    <t>Segue adequadamente a estrutura esperada de relatório analítico, com resumo, consolidação, achados e limitações.</t>
   </si>
   <si>
     <t>Metadados corretos</t>
   </si>
   <si>
-    <t>Informações sobre períodos e arquivos processados estão consistentes.</t>
+    <t>Os períodos e categorias estão corretamente representados, mas há inconsistências numéricas no resultado de junho e agosto e nas margens de junho, agosto e setembro.</t>
   </si>
   <si>
     <t>Llama 8B</t>
   </si>
   <si>
-    <t>Preserva apenas parte das informações centrais. O relatório apresenta recorte temporal mal formulado, ordem dos períodos inconsistente e síntese com distorções relevantes dos dados.</t>
-  </si>
-  <si>
-    <t>Não inventa categorias nem a base temática dos documentos, mas apresenta erros numéricos relevantes em resultados e margens.</t>
-  </si>
-  <si>
-    <t>Resumo ligeiramente mais enxuto, mas ainda apropriado.</t>
-  </si>
-  <si>
-    <t>A fluidez do texto é apenas aparente. A análise é incoerente porque erra a ordem dos períodos, compara dados de forma inadequada e apresenta métricas incorretas.</t>
-  </si>
-  <si>
-    <t>Padrões identificados condizem parcialmente com os balancetes.</t>
-  </si>
-  <si>
-    <t>Parte das conclusões se apoia nos balancetes, mas várias interpretações são generalizadas e algumas dependem de cálculos incorretos.</t>
-  </si>
-  <si>
-    <t>Segue organização semelhante aos demais modelos.</t>
-  </si>
-  <si>
-    <t>Há inconsistências relevantes em métricas consolidadas, incluindo resultados, margens e organização temporal dos períodos analisados.</t>
+    <t>Preserva apenas parte das informações centrais, pois mantém a base temática dos balancetes, mas organiza os períodos fora da ordem cronológica e força leituras de tendência que os dados não sustentam.</t>
+  </si>
+  <si>
+    <t>Não inventa categorias nem estrutura documental, mas apresenta margens imprecisas e organização temporal inadequada.</t>
+  </si>
+  <si>
+    <t>O relatório é conciso e direto, embora a síntese simplifique excessivamente alguns comportamentos da série.</t>
+  </si>
+  <si>
+    <t>A fluidez textual é apenas aparente, pois a análise combina períodos fora de ordem com leituras de tendência e margens imprecisas.</t>
+  </si>
+  <si>
+    <t>Identifica parcialmente os padrões dos dados, mas exagera ao tratar oscilações como tendência de crescimento e ao interpretar a série de forma linear.</t>
+  </si>
+  <si>
+    <t>As conclusões são apenas parcialmente fundamentadas, pois parte da análise depende de leituras temporais e percentuais pouco precisos.</t>
+  </si>
+  <si>
+    <t>Segue a estrutura geral esperada, com seções reconhecíveis e organização compatível com o tipo de relatório solicitado.</t>
+  </si>
+  <si>
+    <t>Há inconsistências relevantes em margens percentuais e na organização temporal dos períodos analisados.</t>
   </si>
   <si>
     <t>Llama 70B</t>
   </si>
   <si>
-    <t>Preserva só parte dos dados. A análise é comprometida por desordem dos períodos e interpretação errada das margens.</t>
-  </si>
-  <si>
-    <t>Não inventa os dados-base, mas apresenta margens imprecisas e usa essas imprecisões para sustentar conclusões analíticas frágeis.</t>
-  </si>
-  <si>
-    <t>Resumo sintético, com boa distribuição de informações.</t>
-  </si>
-  <si>
-    <t>A coerência é apenas aparente: a tabela está fora de ordem cronológica e as conclusões 
-contradizem os próprios números do relatório.</t>
-  </si>
-  <si>
-    <t>O relatório força conclusões. Trata fatos básicos dos balancetes como tendências 
-e diagnósticos sólidos, sem base suficiente nos dados.</t>
-  </si>
-  <si>
-    <t>As conclusões são fracas e mal sustentadas.</t>
-  </si>
-  <si>
-    <t>Segue estrutura esperada de relatório financeiro.</t>
-  </si>
-  <si>
-    <t>Os metadados temporais e a organização dos períodos estão inadequados. 
-A tabela fora de ordem compromete a leitura evolutiva e sustenta comparações 
-mal formuladas.</t>
+    <t>Preserva bem os principais dados dos balancetes e organiza corretamente os períodos, embora acrescente interpretações quantitativas não demonstradas explicitamente, como a estimativa de que salários representariam cerca de 30% das despesas totais.</t>
+  </si>
+  <si>
+    <t>Não inventa os dados-base e apresenta boa aderência documental, mas inclui inferências quantitativas e gerenciais sem demonstração explícita, especialmente ao estimar que a rubrica de salários teria peso de aproximadamente 30% das despesas.</t>
+  </si>
+  <si>
+    <t>O relatório apresenta boa concisão, com síntese clara, estável e compatível com a complexidade dos dados.</t>
+  </si>
+  <si>
+    <t>A coerência interna é boa, com ordem cronológica correta e comparações consistentes, embora persistam interpretações que excedem a evidência direta.</t>
+  </si>
+  <si>
+    <t>Identifica de forma consistente os principais padrões da série, como oscilação dos resultados, recorrência das categorias de gasto e diferença entre melhor e pior período.</t>
+  </si>
+  <si>
+    <t>As conclusões são majoritariamente descritivas e bem fundamentadas, mas os pontos para investigação ainda sugerem otimização e redução de custos de forma parcialmente prescritiva.</t>
+  </si>
+  <si>
+    <t>Segue adequadamente a estrutura esperada, com boa organização das seções e apresentação consistente dos dados.</t>
+  </si>
+  <si>
+    <t>Os metadados temporais e a ordenação dos períodos estão corretos; a principal limitação residual está nas inferências analíticas e em uma quantificação específica incorreta sobre o peso da rubrica de salários nas despesas.</t>
   </si>
 </sst>
 </file>
@@ -206,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -221,13 +217,10 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -505,7 +498,7 @@
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -561,7 +554,7 @@
       <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -575,7 +568,7 @@
       <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -645,7 +638,7 @@
       <c r="C14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -673,7 +666,7 @@
       <c r="C16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>32</v>
       </c>
     </row>
@@ -729,7 +722,7 @@
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -771,7 +764,7 @@
       <c r="C23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -785,7 +778,7 @@
       <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>41</v>
       </c>
     </row>
@@ -799,7 +792,7 @@
       <c r="C25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="6" t="s">
         <v>42</v>
       </c>
     </row>

--- a/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
+++ b/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="41">
   <si>
     <t>Modelo</t>
   </si>
@@ -34,7 +34,7 @@
     <t>Preservação de informações-chave</t>
   </si>
   <si>
-    <t>Preserva os principais pontos dos balancetes e apresenta boa organização analítica, mas contém erros numéricos em junho e agosto, além de pequena imprecisão na margem de setembro, o que compromete parcialmente a comparação entre os períodos.</t>
+    <t>Preserva os principais pontos dos balancetes e apresenta boa organização analítica, mas contém erros numéricos nos resultados em junho e agosto, além de pequena imprecisão na margens de junho, agosto e setembro e , o que compromete parcialmente a comparação entre os períodos.</t>
   </si>
   <si>
     <t>Ausência de informações inventadas</t>
@@ -49,7 +49,7 @@
     <t>Concisão adequada</t>
   </si>
   <si>
-    <t>O relatório apresenta boa concisão, com síntese clara e sem excesso de detalhamento.</t>
+    <t xml:space="preserve">O relatório apresenta boa concisão, com síntese clara e sem excesso de detalhamento. </t>
   </si>
   <si>
     <t>Coerência interna</t>
@@ -64,13 +64,13 @@
     <t>Identificação de padrões válidos</t>
   </si>
   <si>
-    <t>Identifica de forma adequada os padrões gerais da série, como oscilação das receitas, estabilidade relativa das despesas e recorrência de categorias de gasto, embora parte da comparação entre períodos fique comprometida por erros de cálculo.</t>
+    <t>Fez uma boa análise de padrões, sendo parcialmente prejudicada por conta das imprecisões numéricas.</t>
   </si>
   <si>
     <t>Conclusões fundamentadas</t>
   </si>
   <si>
-    <t>As conclusões são cautelosas e bem fundamentadas, com uso de pontos para investigação e explicitação das limitações da análise.</t>
+    <t>As conclusões são bem fundamentadas, mas houve ocasiões onde cometeu equívoco</t>
   </si>
   <si>
     <t>D. Estrutura e Organização</t>
@@ -91,55 +91,49 @@
     <t>Llama 8B</t>
   </si>
   <si>
-    <t>Preserva apenas parte das informações centrais, pois mantém a base temática dos balancetes, mas organiza os períodos fora da ordem cronológica e força leituras de tendência que os dados não sustentam.</t>
-  </si>
-  <si>
-    <t>Não inventa categorias nem estrutura documental, mas apresenta margens imprecisas e organização temporal inadequada.</t>
-  </si>
-  <si>
-    <t>O relatório é conciso e direto, embora a síntese simplifique excessivamente alguns comportamentos da série.</t>
-  </si>
-  <si>
-    <t>A fluidez textual é apenas aparente, pois a análise combina períodos fora de ordem com leituras de tendência e margens imprecisas.</t>
-  </si>
-  <si>
-    <t>Identifica parcialmente os padrões dos dados, mas exagera ao tratar oscilações como tendência de crescimento e ao interpretar a série de forma linear.</t>
-  </si>
-  <si>
-    <t>As conclusões são apenas parcialmente fundamentadas, pois parte da análise depende de leituras temporais e percentuais pouco precisos.</t>
-  </si>
-  <si>
-    <t>Segue a estrutura geral esperada, com seções reconhecíveis e organização compatível com o tipo de relatório solicitado.</t>
-  </si>
-  <si>
-    <t>Há inconsistências relevantes em margens percentuais e na organização temporal dos períodos analisados.</t>
+    <t>Preserva os principais pontos dos balancetes e apresenta boa organização analítica, mas contêm pequena imprecisão nas margens de junho, julho agosto e setembro e erros numéricos nos resultados em junho, o que compromete parcialmente a comparação entre os períodos.</t>
+  </si>
+  <si>
+    <t>Não inventa categorias nem estrutura documental, mas apresenta margens imprecisas e organização temporal inadequada, além de tendência equivocada de crescimento</t>
+  </si>
+  <si>
+    <t>O relatório é conciso e direto.</t>
+  </si>
+  <si>
+    <t>Identifica parcialmente os padrões dos dados, mas exagera ao tratar oscilações como tendência de crescimento.</t>
+  </si>
+  <si>
+    <t>A qualidade das conclusões está parcialmente boa, mas algumas contem exagero e inconsistências</t>
+  </si>
+  <si>
+    <t>Segue a estrutura geral esperada</t>
+  </si>
+  <si>
+    <t>Há leves erros numéricos e em margens percentuais e também há equivocos na detecção de tendencias.</t>
   </si>
   <si>
     <t>Llama 70B</t>
   </si>
   <si>
-    <t>Preserva bem os principais dados dos balancetes e organiza corretamente os períodos, embora acrescente interpretações quantitativas não demonstradas explicitamente, como a estimativa de que salários representariam cerca de 30% das despesas totais.</t>
+    <t>Preserva bem os principais dados dos balancetes e organiza corretamente os períodos, embora acrescente interpretações quantitativas não demonstradas explicitamente, como a estimativa de que salários representam cerca de 30% das despesas totais,além de que contém pequena imprecisão na margens de junho, julho e setembro e , o que compromete parcialmente a comparação entre os períodos</t>
   </si>
   <si>
     <t>Não inventa os dados-base e apresenta boa aderência documental, mas inclui inferências quantitativas e gerenciais sem demonstração explícita, especialmente ao estimar que a rubrica de salários teria peso de aproximadamente 30% das despesas.</t>
   </si>
   <si>
-    <t>O relatório apresenta boa concisão, com síntese clara, estável e compatível com a complexidade dos dados.</t>
-  </si>
-  <si>
-    <t>A coerência interna é boa, com ordem cronológica correta e comparações consistentes, embora persistam interpretações que excedem a evidência direta.</t>
-  </si>
-  <si>
-    <t>Identifica de forma consistente os principais padrões da série, como oscilação dos resultados, recorrência das categorias de gasto e diferença entre melhor e pior período.</t>
-  </si>
-  <si>
-    <t>As conclusões são majoritariamente descritivas e bem fundamentadas, mas os pontos para investigação ainda sugerem otimização e redução de custos de forma parcialmente prescritiva.</t>
+    <t>O relatório apresenta boa concisão, com síntese clara e estável.</t>
+  </si>
+  <si>
+    <t>Faz análises de padrões boas, mas comete erros, como a atribuição de aproximadamente 30% das despesas à rubrica de salários.</t>
+  </si>
+  <si>
+    <t>As conclusões com base nos dados são boas, mas comete erros.</t>
   </si>
   <si>
     <t>Segue adequadamente a estrutura esperada, com boa organização das seções e apresentação consistente dos dados.</t>
   </si>
   <si>
-    <t>Os metadados temporais e a ordenação dos períodos estão corretos; a principal limitação residual está nas inferências analíticas e em uma quantificação específica incorreta sobre o peso da rubrica de salários nas despesas.</t>
+    <t>Os metadados temporais e a ordenação dos períodos estão corretos; Equivocos acontecem nas inferências analíticas e em uma quantificação específica incorreta sobre o peso da rubrica de salários nas despesas. E contém pequena imprecisão em margens de junho, julho e setembro</t>
   </si>
 </sst>
 </file>
@@ -625,7 +619,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -639,7 +633,7 @@
         <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -653,7 +647,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +661,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -681,12 +675,12 @@
         <v>23</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>5</v>
@@ -695,12 +689,12 @@
         <v>6</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>5</v>
@@ -709,12 +703,12 @@
         <v>8</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>10</v>
@@ -723,12 +717,12 @@
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>10</v>
@@ -737,12 +731,12 @@
         <v>13</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -751,12 +745,12 @@
         <v>16</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -765,12 +759,12 @@
         <v>18</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>20</v>
@@ -779,12 +773,12 @@
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>20</v>
@@ -793,7 +787,7 @@
         <v>23</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1"/>

--- a/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
+++ b/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="42">
   <si>
     <t>Modelo</t>
   </si>
@@ -55,49 +55,52 @@
     <t>Coerência interna</t>
   </si>
   <si>
+    <t>O relatório apresenta boa coerência discursiva e linguagem cautelosa. A coerência analítica também é assertiva.</t>
+  </si>
+  <si>
+    <t>C. Qualidade da Análise Consolidada</t>
+  </si>
+  <si>
+    <t>Identificação de padrões válidos</t>
+  </si>
+  <si>
+    <t>Fez uma boa análise de padrões, sendo parcialmente prejudicada por conta das imprecisões numéricas.</t>
+  </si>
+  <si>
+    <t>Conclusões fundamentadas</t>
+  </si>
+  <si>
+    <t>As conclusões são bem fundamentadas, mas houve ocasiões onde cometeu equívoco</t>
+  </si>
+  <si>
+    <t>D. Estrutura e Organização</t>
+  </si>
+  <si>
+    <t>Aderência ao formato</t>
+  </si>
+  <si>
+    <t>Segue adequadamente a estrutura esperada de relatório analítico, com resumo, consolidação, achados e limitações.</t>
+  </si>
+  <si>
+    <t>Metadados corretos</t>
+  </si>
+  <si>
+    <t>Os períodos e categorias estão corretamente representados, mas há inconsistências numéricas no resultado de junho e agosto e nas margens de junho, agosto e setembro.</t>
+  </si>
+  <si>
+    <t>Llama 8B</t>
+  </si>
+  <si>
+    <t>Preserva os principais pontos dos balancetes e apresenta boa organização analítica, mas contêm pequena imprecisão nas margens de junho, julho agosto e setembro e erros numéricos nos resultados em junho.</t>
+  </si>
+  <si>
+    <t>Não inventa categorias nem estrutura documental, mas apresenta margens imprecisas e organização temporal inadequada, além de tendência equivocada de crescimento</t>
+  </si>
+  <si>
+    <t>O relatório é conciso e direto.</t>
+  </si>
+  <si>
     <t>O relatório apresenta boa coerência discursiva e linguagem cautelosa, mas a coerência analítica é parcialmente enfraquecida por erros numéricos que afetam comparações de desempenho.</t>
-  </si>
-  <si>
-    <t>C. Qualidade da Análise Consolidada</t>
-  </si>
-  <si>
-    <t>Identificação de padrões válidos</t>
-  </si>
-  <si>
-    <t>Fez uma boa análise de padrões, sendo parcialmente prejudicada por conta das imprecisões numéricas.</t>
-  </si>
-  <si>
-    <t>Conclusões fundamentadas</t>
-  </si>
-  <si>
-    <t>As conclusões são bem fundamentadas, mas houve ocasiões onde cometeu equívoco</t>
-  </si>
-  <si>
-    <t>D. Estrutura e Organização</t>
-  </si>
-  <si>
-    <t>Aderência ao formato</t>
-  </si>
-  <si>
-    <t>Segue adequadamente a estrutura esperada de relatório analítico, com resumo, consolidação, achados e limitações.</t>
-  </si>
-  <si>
-    <t>Metadados corretos</t>
-  </si>
-  <si>
-    <t>Os períodos e categorias estão corretamente representados, mas há inconsistências numéricas no resultado de junho e agosto e nas margens de junho, agosto e setembro.</t>
-  </si>
-  <si>
-    <t>Llama 8B</t>
-  </si>
-  <si>
-    <t>Preserva os principais pontos dos balancetes e apresenta boa organização analítica, mas contêm pequena imprecisão nas margens de junho, julho agosto e setembro e erros numéricos nos resultados em junho, o que compromete parcialmente a comparação entre os períodos.</t>
-  </si>
-  <si>
-    <t>Não inventa categorias nem estrutura documental, mas apresenta margens imprecisas e organização temporal inadequada, além de tendência equivocada de crescimento</t>
-  </si>
-  <si>
-    <t>O relatório é conciso e direto.</t>
   </si>
   <si>
     <t>Identifica parcialmente os padrões dos dados, mas exagera ao tratar oscilações como tendência de crescimento.</t>
@@ -140,7 +143,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -161,11 +164,6 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -205,16 +203,16 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -506,7 +504,7 @@
       <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -576,7 +574,7 @@
       <c r="C10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -619,7 +617,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -633,7 +631,7 @@
         <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -647,7 +645,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -661,7 +659,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -675,12 +673,12 @@
         <v>23</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>5</v>
@@ -689,12 +687,12 @@
         <v>6</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>5</v>
@@ -703,12 +701,12 @@
         <v>8</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>10</v>
@@ -717,12 +715,12 @@
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>10</v>
@@ -730,13 +728,13 @@
       <c r="C21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="D21" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -744,13 +742,13 @@
       <c r="C22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="D22" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -759,12 +757,12 @@
         <v>18</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>20</v>
@@ -773,12 +771,12 @@
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>20</v>
@@ -786,8 +784,8 @@
       <c r="C25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>40</v>
+      <c r="D25" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1"/>

--- a/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
+++ b/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
   <si>
     <t>Modelo</t>
   </si>
@@ -100,7 +100,8 @@
     <t>O relatório é conciso e direto.</t>
   </si>
   <si>
-    <t>O relatório apresenta boa coerência discursiva e linguagem cautelosa, mas a coerência analítica é parcialmente enfraquecida por erros numéricos que afetam comparações de desempenho.</t>
+    <t xml:space="preserve">O relatório apresenta boa coerência discursiva e linguagem cautelosa, mas a coerência analítica é parcialmente enfraquecida por erros na análise de tendência de crescimento de receita e de resultado.
+</t>
   </si>
   <si>
     <t>Identifica parcialmente os padrões dos dados, mas exagera ao tratar oscilações como tendência de crescimento.</t>
@@ -125,6 +126,10 @@
   </si>
   <si>
     <t>O relatório apresenta boa concisão, com síntese clara e estável.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O relatório apresenta boa coerência discursiva e linguagem cautelosa. A coerência analítica é assertiva, mas tem um pequeno erro de arredondamento nas margens percentuais
+</t>
   </si>
   <si>
     <t>Faz análises de padrões boas, mas comete erros, como a atribuição de aproximadamente 30% das despesas à rubrica de salários.</t>
@@ -209,7 +214,7 @@
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -504,7 +509,7 @@
       <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -574,7 +579,7 @@
       <c r="C10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -616,7 +621,7 @@
       <c r="C13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -718,7 +723,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21">
       <c r="A21" s="2" t="s">
         <v>34</v>
       </c>
@@ -729,10 +734,10 @@
         <v>13</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="2" t="s">
         <v>34</v>
       </c>
@@ -743,10 +748,10 @@
         <v>16</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="2" t="s">
         <v>34</v>
       </c>
@@ -757,10 +762,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="2" t="s">
         <v>34</v>
       </c>
@@ -771,10 +776,10 @@
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="2" t="s">
         <v>34</v>
       </c>
@@ -785,7 +790,7 @@
         <v>23</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1"/>

--- a/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
+++ b/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
@@ -119,10 +119,10 @@
     <t>Llama 70B</t>
   </si>
   <si>
-    <t>Preserva bem os principais dados dos balancetes e organiza corretamente os períodos, embora acrescente interpretações quantitativas não demonstradas explicitamente, como a estimativa de que salários representam cerca de 30% das despesas totais,além de que contém pequena imprecisão na margens de junho, julho e setembro e , o que compromete parcialmente a comparação entre os períodos</t>
-  </si>
-  <si>
-    <t>Não inventa os dados-base e apresenta boa aderência documental, mas inclui inferências quantitativas e gerenciais sem demonstração explícita, especialmente ao estimar que a rubrica de salários teria peso de aproximadamente 30% das despesas.</t>
+    <t>Preserva bem os principais dados dos balancetes e organiza corretamente os períodos, embora acrescente interpretações quantitativas não demonstradas explicitamente, como a estimativa de que salários representam cerca de 30% das despesas totais,além de que contém pequena imprecisão na margens de junho, julho e setembro</t>
+  </si>
+  <si>
+    <t>Não inventa os dados-base e apresenta boa aderência documental, mas faz uma análise errada de que a rubrica de salários teria peso de aproximadamente 30% das despesas.</t>
   </si>
   <si>
     <t>O relatório apresenta boa concisão, com síntese clara e estável.</t>
@@ -214,7 +214,7 @@
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -621,7 +621,7 @@
       <c r="C13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>29</v>
       </c>
     </row>
@@ -691,7 +691,7 @@
       <c r="C18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>35</v>
       </c>
     </row>
@@ -705,7 +705,7 @@
       <c r="C19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>34</v>
       </c>
@@ -737,7 +737,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>34</v>
       </c>
@@ -751,7 +751,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>34</v>
       </c>
@@ -765,7 +765,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>34</v>
       </c>
@@ -779,7 +779,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>34</v>
       </c>

--- a/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
+++ b/checklists/estudo_caso_2/checklist_estudo_caso_2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
   <si>
     <t>Modelo</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Preserva os principais pontos dos balancetes e apresenta boa organização analítica, mas contém erros numéricos nos resultados em junho e agosto, além de pequena imprecisão na margens de junho, agosto e setembro e , o que compromete parcialmente a comparação entre os períodos.</t>
   </si>
   <si>
-    <t>Ausência de informações inventadas</t>
+    <t>Ausência de alucinações</t>
   </si>
   <si>
     <t>Não inventa categorias, períodos ou estrutura documental, mas apresenta incorreções parciais nos valores consolidados: resultado e margem em junho e agosto, além de pequena imprecisão na margem de setembro.</t>
@@ -55,7 +55,7 @@
     <t>Coerência interna</t>
   </si>
   <si>
-    <t>O relatório apresenta boa coerência discursiva e linguagem cautelosa, mas a coerência analítica é parcialmente enfraquecida por erros numéricos que afetam comparações de desempenho.</t>
+    <t>O relatório apresenta boa coerência discursiva e linguagem cautelosa. A coerência analítica também é assertiva.</t>
   </si>
   <si>
     <t>C. Qualidade da Análise Consolidada</t>
@@ -91,7 +91,7 @@
     <t>Llama 8B</t>
   </si>
   <si>
-    <t>Preserva os principais pontos dos balancetes e apresenta boa organização analítica, mas contêm pequena imprecisão nas margens de junho, julho agosto e setembro e erros numéricos nos resultados em junho, o que compromete parcialmente a comparação entre os períodos.</t>
+    <t>Preserva os principais pontos dos balancetes e apresenta boa organização analítica, mas contêm pequena imprecisão nas margens de junho, julho agosto e setembro e erros numéricos nos resultados em junho.</t>
   </si>
   <si>
     <t>Não inventa categorias nem estrutura documental, mas apresenta margens imprecisas e organização temporal inadequada, além de tendência equivocada de crescimento</t>
@@ -100,6 +100,10 @@
     <t>O relatório é conciso e direto.</t>
   </si>
   <si>
+    <t xml:space="preserve">O relatório apresenta boa coerência discursiva e linguagem cautelosa, mas a coerência analítica é parcialmente enfraquecida por erros na análise de tendência de crescimento de receita e de resultado.
+</t>
+  </si>
+  <si>
     <t>Identifica parcialmente os padrões dos dados, mas exagera ao tratar oscilações como tendência de crescimento.</t>
   </si>
   <si>
@@ -115,13 +119,17 @@
     <t>Llama 70B</t>
   </si>
   <si>
-    <t>Preserva bem os principais dados dos balancetes e organiza corretamente os períodos, embora acrescente interpretações quantitativas não demonstradas explicitamente, como a estimativa de que salários representam cerca de 30% das despesas totais,além de que contém pequena imprecisão na margens de junho, julho e setembro e , o que compromete parcialmente a comparação entre os períodos</t>
-  </si>
-  <si>
-    <t>Não inventa os dados-base e apresenta boa aderência documental, mas inclui inferências quantitativas e gerenciais sem demonstração explícita, especialmente ao estimar que a rubrica de salários teria peso de aproximadamente 30% das despesas.</t>
+    <t>Preserva bem os principais dados dos balancetes e organiza corretamente os períodos, embora acrescente interpretações quantitativas não demonstradas explicitamente, como a estimativa de que salários representam cerca de 30% das despesas totais,além de que contém pequena imprecisão na margens de junho, julho e setembro</t>
+  </si>
+  <si>
+    <t>Não inventa os dados-base e apresenta boa aderência documental, mas faz uma análise errada de que a rubrica de salários teria peso de aproximadamente 30% das despesas.</t>
   </si>
   <si>
     <t>O relatório apresenta boa concisão, com síntese clara e estável.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O relatório apresenta boa coerência discursiva e linguagem cautelosa. A coerência analítica é assertiva, mas tem um pequeno erro de arredondamento nas margens percentuais
+</t>
   </si>
   <si>
     <t>Faz análises de padrões boas, mas comete erros, como a atribuição de aproximadamente 30% das despesas à rubrica de salários.</t>
@@ -140,7 +148,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -161,11 +169,6 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -205,16 +208,16 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,7 +478,7 @@
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -587,7 +590,7 @@
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -619,7 +622,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -633,7 +636,7 @@
         <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -647,7 +650,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -661,7 +664,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -675,12 +678,12 @@
         <v>23</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>5</v>
@@ -689,26 +692,26 @@
         <v>6</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>10</v>
@@ -717,12 +720,12 @@
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>10</v>
@@ -730,13 +733,13 @@
       <c r="C21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="D21" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -744,13 +747,13 @@
       <c r="C22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="D22" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -759,12 +762,12 @@
         <v>18</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>20</v>
@@ -773,12 +776,12 @@
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>20</v>
@@ -786,8 +789,8 @@
       <c r="C25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>40</v>
+      <c r="D25" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1"/>
